--- a/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_schedulables.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_schedulables.xlsx
@@ -597,7 +597,7 @@
         <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
         <v>50</v>
@@ -617,7 +617,7 @@
         <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
@@ -637,7 +637,7 @@
         <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
         <v>50</v>
@@ -654,10 +654,10 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F12" t="n">
         <v>50</v>
@@ -674,10 +674,10 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
         <v>50</v>
@@ -688,16 +688,16 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F14" t="n">
         <v>50</v>
@@ -714,10 +714,10 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F15" t="n">
         <v>49</v>
@@ -734,13 +734,13 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -748,16 +748,16 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E17" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F17" t="n">
         <v>45</v>
@@ -768,19 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" t="n">
         <v>41</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -808,19 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -828,19 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_schedulables.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_schedulables.xlsx
@@ -577,7 +577,7 @@
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
         <v>50</v>
@@ -614,10 +614,10 @@
         <v>50</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
@@ -637,7 +637,7 @@
         <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
         <v>50</v>
@@ -674,10 +674,10 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
         <v>50</v>
@@ -688,19 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
+        <v>48</v>
+      </c>
+      <c r="C14" t="n">
+        <v>48</v>
+      </c>
+      <c r="D14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F14" t="n">
         <v>49</v>
-      </c>
-      <c r="C14" t="n">
-        <v>49</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48</v>
-      </c>
-      <c r="E14" t="n">
-        <v>39</v>
-      </c>
-      <c r="F14" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -708,19 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -728,19 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -754,13 +754,13 @@
         <v>44</v>
       </c>
       <c r="D17" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
@@ -768,19 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -808,16 +808,16 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
         <v>34</v>
@@ -828,19 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
